--- a/backend/templates/pre-store-form.xlsx
+++ b/backend/templates/pre-store-form.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Cursor AI Projects\SwansonIndiaPortal\backend\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C754F347-B71F-498F-B650-A023480C07A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C16EF943-EE50-404E-A508-AD1F4AD09131}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Pre-Store Inspection Form" sheetId="8" r:id="rId1"/>
@@ -19,6 +19,11 @@
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Pre-Store Inspection Form'!$A$1:$V$36</definedName>
   </definedNames>
   <calcPr calcId="145621"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -915,457 +920,427 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="151">
+  <cellXfs count="141">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="5" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1674,1024 +1649,1062 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AF36"/>
+  <dimension ref="A1:AF35"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24" style="2" customWidth="1"/>
-    <col min="2" max="2" width="8.42578125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="11.42578125" style="2" customWidth="1"/>
-    <col min="4" max="4" width="4.28515625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="1" style="2" customWidth="1"/>
-    <col min="6" max="6" width="12.85546875" style="2" customWidth="1"/>
-    <col min="7" max="7" width="7.140625" style="2" customWidth="1"/>
-    <col min="8" max="8" width="4.42578125" style="2" customWidth="1"/>
-    <col min="9" max="9" width="0.85546875" style="2" customWidth="1"/>
-    <col min="10" max="10" width="15" style="2" customWidth="1"/>
-    <col min="11" max="11" width="7.5703125" style="2" customWidth="1"/>
-    <col min="12" max="12" width="2.140625" style="2" customWidth="1"/>
-    <col min="13" max="13" width="5.28515625" style="2" customWidth="1"/>
-    <col min="14" max="14" width="9.85546875" style="2" customWidth="1"/>
-    <col min="15" max="15" width="15" style="2" customWidth="1"/>
-    <col min="16" max="16" width="17.85546875" style="2" customWidth="1"/>
-    <col min="17" max="17" width="2.140625" style="2" customWidth="1"/>
-    <col min="18" max="18" width="5.42578125" style="2" customWidth="1"/>
-    <col min="19" max="19" width="7.140625" style="2" customWidth="1"/>
-    <col min="20" max="20" width="7.7109375" style="2" customWidth="1"/>
-    <col min="21" max="21" width="13.85546875" style="2" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="2" customWidth="1"/>
-    <col min="23" max="23" width="25.5703125" style="2" customWidth="1"/>
-    <col min="24" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="1" width="24" style="1" customWidth="1"/>
+    <col min="2" max="2" width="8.42578125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="11.42578125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="4.28515625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="1" style="1" customWidth="1"/>
+    <col min="6" max="6" width="12.85546875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="7.140625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="4.42578125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="0.85546875" style="1" customWidth="1"/>
+    <col min="10" max="10" width="15" style="1" customWidth="1"/>
+    <col min="11" max="11" width="7.5703125" style="1" customWidth="1"/>
+    <col min="12" max="12" width="2.140625" style="1" customWidth="1"/>
+    <col min="13" max="13" width="5.28515625" style="1" customWidth="1"/>
+    <col min="14" max="14" width="9.85546875" style="1" customWidth="1"/>
+    <col min="15" max="15" width="15" style="1" customWidth="1"/>
+    <col min="16" max="16" width="17.85546875" style="1" customWidth="1"/>
+    <col min="17" max="17" width="2.140625" style="1" customWidth="1"/>
+    <col min="18" max="18" width="5.42578125" style="1" customWidth="1"/>
+    <col min="19" max="19" width="7.140625" style="1" customWidth="1"/>
+    <col min="20" max="20" width="7.7109375" style="1" customWidth="1"/>
+    <col min="21" max="21" width="13.85546875" style="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" customWidth="1"/>
+    <col min="23" max="23" width="25.5703125" style="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="66" t="s">
+      <c r="A1" s="35" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="66"/>
-      <c r="C1" s="66"/>
-      <c r="D1" s="66"/>
-      <c r="E1" s="66"/>
-      <c r="F1" s="66"/>
-      <c r="G1" s="66"/>
-      <c r="H1" s="66"/>
-      <c r="I1" s="66"/>
-      <c r="J1" s="66"/>
-      <c r="K1" s="66"/>
-      <c r="L1" s="66"/>
-      <c r="M1" s="66"/>
-      <c r="N1" s="66"/>
-      <c r="O1" s="66"/>
-      <c r="P1" s="66"/>
-      <c r="Q1" s="66"/>
-      <c r="R1" s="66"/>
-      <c r="S1" s="66"/>
-      <c r="T1" s="66"/>
-      <c r="U1" s="66"/>
-      <c r="V1" s="66"/>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="35"/>
+      <c r="H1" s="35"/>
+      <c r="I1" s="35"/>
+      <c r="J1" s="35"/>
+      <c r="K1" s="35"/>
+      <c r="L1" s="35"/>
+      <c r="M1" s="35"/>
+      <c r="N1" s="35"/>
+      <c r="O1" s="35"/>
+      <c r="P1" s="35"/>
+      <c r="Q1" s="35"/>
+      <c r="R1" s="35"/>
+      <c r="S1" s="35"/>
+      <c r="T1" s="35"/>
+      <c r="U1" s="35"/>
+      <c r="V1" s="35"/>
     </row>
     <row r="2" spans="1:32" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="121" t="s">
+      <c r="A2" s="40" t="s">
         <v>35</v>
       </c>
-      <c r="B2" s="121"/>
-      <c r="C2" s="121"/>
-      <c r="D2" s="121"/>
-      <c r="E2" s="121"/>
-      <c r="F2" s="121"/>
-      <c r="G2" s="121"/>
-      <c r="H2" s="121"/>
-      <c r="I2" s="121"/>
-      <c r="J2" s="121"/>
-      <c r="K2" s="121"/>
-      <c r="L2" s="121"/>
-      <c r="M2" s="121"/>
-      <c r="N2" s="121"/>
-      <c r="O2" s="121"/>
-      <c r="P2" s="121"/>
-      <c r="Q2" s="121"/>
-      <c r="R2" s="121"/>
-      <c r="S2" s="121"/>
-      <c r="T2" s="121"/>
-      <c r="U2" s="121"/>
-      <c r="V2" s="121"/>
+      <c r="B2" s="40"/>
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="40"/>
+      <c r="G2" s="40"/>
+      <c r="H2" s="40"/>
+      <c r="I2" s="40"/>
+      <c r="J2" s="40"/>
+      <c r="K2" s="40"/>
+      <c r="L2" s="40"/>
+      <c r="M2" s="40"/>
+      <c r="N2" s="40"/>
+      <c r="O2" s="40"/>
+      <c r="P2" s="40"/>
+      <c r="Q2" s="40"/>
+      <c r="R2" s="40"/>
+      <c r="S2" s="40"/>
+      <c r="T2" s="40"/>
+      <c r="U2" s="40"/>
+      <c r="V2" s="40"/>
     </row>
     <row r="3" spans="1:32" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="31"/>
-      <c r="B3" s="31"/>
-      <c r="C3" s="31"/>
-      <c r="D3" s="31"/>
-      <c r="E3" s="31"/>
-      <c r="F3" s="31"/>
-      <c r="G3" s="31"/>
-      <c r="H3" s="31"/>
-      <c r="I3" s="31"/>
-      <c r="J3" s="31"/>
-      <c r="K3" s="31"/>
-      <c r="L3" s="31"/>
-      <c r="M3" s="31"/>
-      <c r="N3" s="31"/>
-      <c r="O3" s="31"/>
-      <c r="P3" s="31"/>
-      <c r="Q3" s="31"/>
-      <c r="R3" s="31"/>
-      <c r="S3" s="31"/>
-      <c r="T3" s="30" t="s">
+      <c r="A3" s="41"/>
+      <c r="B3" s="41"/>
+      <c r="C3" s="41"/>
+      <c r="D3" s="41"/>
+      <c r="E3" s="41"/>
+      <c r="F3" s="41"/>
+      <c r="G3" s="41"/>
+      <c r="H3" s="41"/>
+      <c r="I3" s="41"/>
+      <c r="J3" s="41"/>
+      <c r="K3" s="41"/>
+      <c r="L3" s="41"/>
+      <c r="M3" s="41"/>
+      <c r="N3" s="41"/>
+      <c r="O3" s="41"/>
+      <c r="P3" s="41"/>
+      <c r="Q3" s="41"/>
+      <c r="R3" s="41"/>
+      <c r="S3" s="41"/>
+      <c r="T3" s="42" t="s">
         <v>38</v>
       </c>
-      <c r="U3" s="30"/>
-      <c r="V3" s="21"/>
+      <c r="U3" s="42"/>
+      <c r="V3" s="43"/>
     </row>
     <row r="4" spans="1:32" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="29" t="s">
+      <c r="A4" s="44" t="s">
         <v>44</v>
       </c>
-      <c r="B4" s="51"/>
-      <c r="C4" s="52"/>
-      <c r="D4" s="53"/>
-      <c r="E4" s="47" t="s">
+      <c r="B4" s="45"/>
+      <c r="C4" s="46"/>
+      <c r="D4" s="47"/>
+      <c r="E4" s="48" t="s">
         <v>22</v>
       </c>
-      <c r="F4" s="48"/>
-      <c r="G4" s="51"/>
-      <c r="H4" s="52"/>
-      <c r="I4" s="52"/>
-      <c r="J4" s="52"/>
-      <c r="K4" s="53"/>
-      <c r="L4" s="41" t="s">
+      <c r="F4" s="49"/>
+      <c r="G4" s="45"/>
+      <c r="H4" s="46"/>
+      <c r="I4" s="46"/>
+      <c r="J4" s="46"/>
+      <c r="K4" s="47"/>
+      <c r="L4" s="50" t="s">
         <v>0</v>
       </c>
-      <c r="M4" s="42"/>
-      <c r="N4" s="43"/>
-      <c r="O4" s="58"/>
-      <c r="P4" s="58"/>
-      <c r="Q4" s="41" t="s">
+      <c r="M4" s="51"/>
+      <c r="N4" s="52"/>
+      <c r="O4" s="53"/>
+      <c r="P4" s="53"/>
+      <c r="Q4" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="R4" s="42"/>
-      <c r="S4" s="43"/>
-      <c r="T4" s="58"/>
-      <c r="U4" s="51"/>
-      <c r="V4" s="114"/>
-      <c r="W4" s="3"/>
+      <c r="R4" s="51"/>
+      <c r="S4" s="52"/>
+      <c r="T4" s="53"/>
+      <c r="U4" s="45"/>
+      <c r="V4" s="54"/>
+      <c r="W4" s="55"/>
     </row>
     <row r="5" spans="1:32" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="56" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="119"/>
-      <c r="C5" s="104"/>
-      <c r="D5" s="120"/>
-      <c r="E5" s="49" t="s">
+      <c r="B5" s="57"/>
+      <c r="C5" s="58"/>
+      <c r="D5" s="59"/>
+      <c r="E5" s="60" t="s">
         <v>3</v>
       </c>
-      <c r="F5" s="50"/>
-      <c r="G5" s="119"/>
-      <c r="H5" s="104"/>
-      <c r="I5" s="104"/>
-      <c r="J5" s="104"/>
-      <c r="K5" s="120"/>
-      <c r="L5" s="44" t="s">
+      <c r="F5" s="61"/>
+      <c r="G5" s="57"/>
+      <c r="H5" s="58"/>
+      <c r="I5" s="58"/>
+      <c r="J5" s="58"/>
+      <c r="K5" s="59"/>
+      <c r="L5" s="62" t="s">
         <v>4</v>
       </c>
-      <c r="M5" s="45"/>
-      <c r="N5" s="46"/>
-      <c r="O5" s="56"/>
-      <c r="P5" s="56"/>
-      <c r="Q5" s="44" t="s">
+      <c r="M5" s="63"/>
+      <c r="N5" s="64"/>
+      <c r="O5" s="65"/>
+      <c r="P5" s="65"/>
+      <c r="Q5" s="62" t="s">
         <v>23</v>
       </c>
-      <c r="R5" s="45"/>
-      <c r="S5" s="46"/>
-      <c r="T5" s="56"/>
-      <c r="U5" s="119"/>
-      <c r="V5" s="138"/>
-      <c r="W5" s="3"/>
+      <c r="R5" s="63"/>
+      <c r="S5" s="64"/>
+      <c r="T5" s="65"/>
+      <c r="U5" s="57"/>
+      <c r="V5" s="66"/>
+      <c r="W5" s="55"/>
     </row>
     <row r="6" spans="1:32" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="22" t="s">
+      <c r="A6" s="67" t="s">
         <v>43</v>
       </c>
-      <c r="B6" s="110"/>
-      <c r="C6" s="111"/>
-      <c r="D6" s="111"/>
-      <c r="E6" s="111"/>
-      <c r="F6" s="111"/>
-      <c r="G6" s="111"/>
-      <c r="H6" s="111"/>
-      <c r="I6" s="111"/>
-      <c r="J6" s="111"/>
-      <c r="K6" s="111"/>
-      <c r="L6" s="111"/>
-      <c r="M6" s="111"/>
-      <c r="N6" s="113"/>
-      <c r="O6" s="23" t="s">
+      <c r="B6" s="68"/>
+      <c r="C6" s="69"/>
+      <c r="D6" s="69"/>
+      <c r="E6" s="69"/>
+      <c r="F6" s="69"/>
+      <c r="G6" s="69"/>
+      <c r="H6" s="69"/>
+      <c r="I6" s="69"/>
+      <c r="J6" s="69"/>
+      <c r="K6" s="69"/>
+      <c r="L6" s="69"/>
+      <c r="M6" s="69"/>
+      <c r="N6" s="70"/>
+      <c r="O6" s="71" t="s">
         <v>14</v>
       </c>
-      <c r="P6" s="110"/>
-      <c r="Q6" s="111"/>
-      <c r="R6" s="111"/>
-      <c r="S6" s="111"/>
-      <c r="T6" s="111"/>
-      <c r="U6" s="111"/>
-      <c r="V6" s="112"/>
+      <c r="P6" s="68"/>
+      <c r="Q6" s="69"/>
+      <c r="R6" s="69"/>
+      <c r="S6" s="69"/>
+      <c r="T6" s="69"/>
+      <c r="U6" s="69"/>
+      <c r="V6" s="72"/>
     </row>
     <row r="7" spans="1:32" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="115" t="s">
+      <c r="A7" s="73" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="116"/>
-      <c r="C7" s="116"/>
-      <c r="D7" s="116"/>
-      <c r="E7" s="116"/>
-      <c r="F7" s="116"/>
-      <c r="G7" s="116"/>
-      <c r="H7" s="116"/>
-      <c r="I7" s="116"/>
-      <c r="J7" s="116"/>
-      <c r="K7" s="116"/>
-      <c r="L7" s="116"/>
-      <c r="M7" s="116"/>
-      <c r="N7" s="116"/>
-      <c r="O7" s="116"/>
-      <c r="P7" s="116"/>
-      <c r="Q7" s="116"/>
-      <c r="R7" s="116"/>
-      <c r="S7" s="116"/>
-      <c r="T7" s="116"/>
-      <c r="U7" s="117"/>
-      <c r="V7" s="118"/>
-      <c r="W7" s="4"/>
-      <c r="X7" s="3"/>
-      <c r="Y7" s="3"/>
-      <c r="Z7" s="3"/>
-      <c r="AA7" s="3"/>
-      <c r="AB7" s="3"/>
-      <c r="AC7" s="3"/>
-      <c r="AD7" s="3"/>
-      <c r="AE7" s="3"/>
-      <c r="AF7" s="3"/>
+      <c r="B7" s="74"/>
+      <c r="C7" s="74"/>
+      <c r="D7" s="74"/>
+      <c r="E7" s="74"/>
+      <c r="F7" s="74"/>
+      <c r="G7" s="74"/>
+      <c r="H7" s="74"/>
+      <c r="I7" s="74"/>
+      <c r="J7" s="74"/>
+      <c r="K7" s="74"/>
+      <c r="L7" s="74"/>
+      <c r="M7" s="74"/>
+      <c r="N7" s="74"/>
+      <c r="O7" s="74"/>
+      <c r="P7" s="74"/>
+      <c r="Q7" s="74"/>
+      <c r="R7" s="74"/>
+      <c r="S7" s="74"/>
+      <c r="T7" s="74"/>
+      <c r="U7" s="75"/>
+      <c r="V7" s="76"/>
+      <c r="W7" s="77"/>
+      <c r="X7" s="55"/>
+      <c r="Y7" s="55"/>
+      <c r="Z7" s="55"/>
+      <c r="AA7" s="55"/>
+      <c r="AB7" s="55"/>
+      <c r="AC7" s="55"/>
+      <c r="AD7" s="55"/>
+      <c r="AE7" s="55"/>
+      <c r="AF7" s="55"/>
     </row>
     <row r="8" spans="1:32" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="108" t="s">
+      <c r="A8" s="78" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="109"/>
-      <c r="C8" s="32" t="s">
+      <c r="B8" s="79"/>
+      <c r="C8" s="80" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="33"/>
-      <c r="E8" s="33"/>
-      <c r="F8" s="33"/>
-      <c r="G8" s="33"/>
-      <c r="H8" s="33"/>
-      <c r="I8" s="33"/>
-      <c r="J8" s="33"/>
-      <c r="K8" s="34"/>
-      <c r="L8" s="58" t="s">
+      <c r="D8" s="81"/>
+      <c r="E8" s="81"/>
+      <c r="F8" s="81"/>
+      <c r="G8" s="81"/>
+      <c r="H8" s="81"/>
+      <c r="I8" s="81"/>
+      <c r="J8" s="81"/>
+      <c r="K8" s="82"/>
+      <c r="L8" s="53" t="s">
         <v>1</v>
       </c>
-      <c r="M8" s="58"/>
-      <c r="N8" s="58"/>
-      <c r="O8" s="58"/>
-      <c r="P8" s="58" t="s">
+      <c r="M8" s="53"/>
+      <c r="N8" s="53"/>
+      <c r="O8" s="53"/>
+      <c r="P8" s="53" t="s">
         <v>8</v>
       </c>
-      <c r="Q8" s="58"/>
-      <c r="R8" s="58"/>
-      <c r="S8" s="58"/>
-      <c r="T8" s="58"/>
-      <c r="U8" s="51"/>
-      <c r="V8" s="114"/>
+      <c r="Q8" s="53"/>
+      <c r="R8" s="53"/>
+      <c r="S8" s="53"/>
+      <c r="T8" s="53"/>
+      <c r="U8" s="45"/>
+      <c r="V8" s="54"/>
     </row>
     <row r="9" spans="1:32" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="54" t="s">
+      <c r="A9" s="83" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="48"/>
-      <c r="C9" s="38"/>
-      <c r="D9" s="39"/>
-      <c r="E9" s="39"/>
-      <c r="F9" s="39"/>
-      <c r="G9" s="39"/>
-      <c r="H9" s="39"/>
-      <c r="I9" s="39"/>
-      <c r="J9" s="39"/>
-      <c r="K9" s="40"/>
-      <c r="L9" s="139" t="s">
+      <c r="B9" s="49"/>
+      <c r="C9" s="84"/>
+      <c r="D9" s="85"/>
+      <c r="E9" s="85"/>
+      <c r="F9" s="85"/>
+      <c r="G9" s="85"/>
+      <c r="H9" s="85"/>
+      <c r="I9" s="85"/>
+      <c r="J9" s="85"/>
+      <c r="K9" s="86"/>
+      <c r="L9" s="87" t="s">
         <v>25</v>
       </c>
-      <c r="M9" s="139"/>
-      <c r="N9" s="139"/>
-      <c r="O9" s="139"/>
-      <c r="P9" s="59"/>
-      <c r="Q9" s="59"/>
-      <c r="R9" s="59"/>
-      <c r="S9" s="59"/>
-      <c r="T9" s="59"/>
-      <c r="U9" s="38"/>
-      <c r="V9" s="60"/>
-      <c r="X9" s="3"/>
-      <c r="Y9" s="3"/>
-      <c r="Z9" s="3"/>
-      <c r="AA9" s="3"/>
-      <c r="AB9" s="3"/>
+      <c r="M9" s="87"/>
+      <c r="N9" s="87"/>
+      <c r="O9" s="87"/>
+      <c r="P9" s="88"/>
+      <c r="Q9" s="88"/>
+      <c r="R9" s="88"/>
+      <c r="S9" s="88"/>
+      <c r="T9" s="88"/>
+      <c r="U9" s="84"/>
+      <c r="V9" s="89"/>
+      <c r="X9" s="55"/>
+      <c r="Y9" s="55"/>
+      <c r="Z9" s="55"/>
+      <c r="AA9" s="55"/>
+      <c r="AB9" s="55"/>
     </row>
     <row r="10" spans="1:32" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="55" t="s">
+      <c r="A10" s="90" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="50"/>
-      <c r="C10" s="35"/>
-      <c r="D10" s="36"/>
-      <c r="E10" s="36"/>
-      <c r="F10" s="36"/>
-      <c r="G10" s="36"/>
-      <c r="H10" s="36"/>
-      <c r="I10" s="36"/>
-      <c r="J10" s="36"/>
-      <c r="K10" s="37"/>
-      <c r="L10" s="57" t="s">
+      <c r="B10" s="61"/>
+      <c r="C10" s="91"/>
+      <c r="D10" s="92"/>
+      <c r="E10" s="92"/>
+      <c r="F10" s="92"/>
+      <c r="G10" s="92"/>
+      <c r="H10" s="92"/>
+      <c r="I10" s="92"/>
+      <c r="J10" s="92"/>
+      <c r="K10" s="93"/>
+      <c r="L10" s="94" t="s">
         <v>5</v>
       </c>
-      <c r="M10" s="57"/>
-      <c r="N10" s="57"/>
-      <c r="O10" s="57"/>
-      <c r="P10" s="70"/>
-      <c r="Q10" s="70"/>
-      <c r="R10" s="70"/>
-      <c r="S10" s="70"/>
-      <c r="T10" s="70"/>
-      <c r="U10" s="35"/>
-      <c r="V10" s="71"/>
+      <c r="M10" s="94"/>
+      <c r="N10" s="94"/>
+      <c r="O10" s="94"/>
+      <c r="P10" s="95"/>
+      <c r="Q10" s="95"/>
+      <c r="R10" s="95"/>
+      <c r="S10" s="95"/>
+      <c r="T10" s="95"/>
+      <c r="U10" s="91"/>
+      <c r="V10" s="96"/>
     </row>
     <row r="11" spans="1:32" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="55" t="s">
+      <c r="A11" s="90" t="s">
         <v>16</v>
       </c>
-      <c r="B11" s="50"/>
-      <c r="C11" s="35"/>
-      <c r="D11" s="36"/>
-      <c r="E11" s="36"/>
-      <c r="F11" s="36"/>
-      <c r="G11" s="36"/>
-      <c r="H11" s="36"/>
-      <c r="I11" s="36"/>
-      <c r="J11" s="36"/>
-      <c r="K11" s="37"/>
-      <c r="L11" s="57" t="s">
+      <c r="B11" s="61"/>
+      <c r="C11" s="91"/>
+      <c r="D11" s="92"/>
+      <c r="E11" s="92"/>
+      <c r="F11" s="92"/>
+      <c r="G11" s="92"/>
+      <c r="H11" s="92"/>
+      <c r="I11" s="92"/>
+      <c r="J11" s="92"/>
+      <c r="K11" s="93"/>
+      <c r="L11" s="94" t="s">
         <v>7</v>
       </c>
-      <c r="M11" s="57"/>
-      <c r="N11" s="57"/>
-      <c r="O11" s="57"/>
-      <c r="P11" s="70"/>
-      <c r="Q11" s="70"/>
-      <c r="R11" s="70"/>
-      <c r="S11" s="70"/>
-      <c r="T11" s="70"/>
-      <c r="U11" s="35"/>
-      <c r="V11" s="71"/>
+      <c r="M11" s="94"/>
+      <c r="N11" s="94"/>
+      <c r="O11" s="94"/>
+      <c r="P11" s="95"/>
+      <c r="Q11" s="95"/>
+      <c r="R11" s="95"/>
+      <c r="S11" s="95"/>
+      <c r="T11" s="95"/>
+      <c r="U11" s="91"/>
+      <c r="V11" s="96"/>
     </row>
     <row r="12" spans="1:32" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="143" t="s">
+      <c r="A12" s="97" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="144"/>
-      <c r="C12" s="145"/>
-      <c r="D12" s="146"/>
-      <c r="E12" s="146"/>
-      <c r="F12" s="146"/>
-      <c r="G12" s="146"/>
-      <c r="H12" s="146"/>
-      <c r="I12" s="146"/>
-      <c r="J12" s="146"/>
-      <c r="K12" s="147"/>
-      <c r="L12" s="148" t="s">
+      <c r="B12" s="98"/>
+      <c r="C12" s="99"/>
+      <c r="D12" s="100"/>
+      <c r="E12" s="100"/>
+      <c r="F12" s="100"/>
+      <c r="G12" s="100"/>
+      <c r="H12" s="100"/>
+      <c r="I12" s="100"/>
+      <c r="J12" s="100"/>
+      <c r="K12" s="101"/>
+      <c r="L12" s="102" t="s">
         <v>6</v>
       </c>
-      <c r="M12" s="148"/>
-      <c r="N12" s="148"/>
-      <c r="O12" s="148"/>
-      <c r="P12" s="149"/>
-      <c r="Q12" s="149"/>
-      <c r="R12" s="149"/>
-      <c r="S12" s="149"/>
-      <c r="T12" s="149"/>
-      <c r="U12" s="145"/>
-      <c r="V12" s="150"/>
+      <c r="M12" s="102"/>
+      <c r="N12" s="102"/>
+      <c r="O12" s="102"/>
+      <c r="P12" s="103"/>
+      <c r="Q12" s="103"/>
+      <c r="R12" s="103"/>
+      <c r="S12" s="103"/>
+      <c r="T12" s="103"/>
+      <c r="U12" s="99"/>
+      <c r="V12" s="104"/>
     </row>
     <row r="13" spans="1:32" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="140" t="s">
+      <c r="A13" s="24" t="s">
         <v>17</v>
       </c>
-      <c r="B13" s="141"/>
-      <c r="C13" s="141"/>
-      <c r="D13" s="141"/>
-      <c r="E13" s="141"/>
-      <c r="F13" s="141"/>
-      <c r="G13" s="141"/>
-      <c r="H13" s="141"/>
-      <c r="I13" s="141"/>
-      <c r="J13" s="141"/>
-      <c r="K13" s="141"/>
-      <c r="L13" s="141"/>
-      <c r="M13" s="141"/>
-      <c r="N13" s="141"/>
-      <c r="O13" s="141"/>
-      <c r="P13" s="141"/>
-      <c r="Q13" s="141"/>
-      <c r="R13" s="141"/>
-      <c r="S13" s="141"/>
-      <c r="T13" s="141"/>
-      <c r="U13" s="141"/>
-      <c r="V13" s="142"/>
+      <c r="B13" s="25"/>
+      <c r="C13" s="25"/>
+      <c r="D13" s="25"/>
+      <c r="E13" s="25"/>
+      <c r="F13" s="25"/>
+      <c r="G13" s="25"/>
+      <c r="H13" s="25"/>
+      <c r="I13" s="25"/>
+      <c r="J13" s="25"/>
+      <c r="K13" s="25"/>
+      <c r="L13" s="25"/>
+      <c r="M13" s="25"/>
+      <c r="N13" s="25"/>
+      <c r="O13" s="25"/>
+      <c r="P13" s="25"/>
+      <c r="Q13" s="25"/>
+      <c r="R13" s="25"/>
+      <c r="S13" s="25"/>
+      <c r="T13" s="25"/>
+      <c r="U13" s="25"/>
+      <c r="V13" s="33"/>
     </row>
     <row r="14" spans="1:32" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="72"/>
-      <c r="B14" s="73"/>
-      <c r="C14" s="73"/>
-      <c r="D14" s="73"/>
-      <c r="E14" s="73"/>
-      <c r="F14" s="73"/>
-      <c r="G14" s="73"/>
-      <c r="H14" s="73"/>
-      <c r="I14" s="73"/>
-      <c r="J14" s="73"/>
-      <c r="K14" s="73"/>
-      <c r="L14" s="73"/>
-      <c r="M14" s="73"/>
-      <c r="N14" s="73"/>
-      <c r="O14" s="73"/>
-      <c r="P14" s="73"/>
-      <c r="Q14" s="73"/>
-      <c r="R14" s="73"/>
-      <c r="S14" s="73"/>
-      <c r="T14" s="73"/>
-      <c r="U14" s="74"/>
-      <c r="V14" s="75"/>
+      <c r="A14" s="105"/>
+      <c r="B14" s="106"/>
+      <c r="C14" s="106"/>
+      <c r="D14" s="106"/>
+      <c r="E14" s="106"/>
+      <c r="F14" s="106"/>
+      <c r="G14" s="106"/>
+      <c r="H14" s="106"/>
+      <c r="I14" s="106"/>
+      <c r="J14" s="106"/>
+      <c r="K14" s="106"/>
+      <c r="L14" s="106"/>
+      <c r="M14" s="106"/>
+      <c r="N14" s="106"/>
+      <c r="O14" s="106"/>
+      <c r="P14" s="106"/>
+      <c r="Q14" s="106"/>
+      <c r="R14" s="106"/>
+      <c r="S14" s="106"/>
+      <c r="T14" s="106"/>
+      <c r="U14" s="107"/>
+      <c r="V14" s="108"/>
     </row>
     <row r="15" spans="1:32" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="76"/>
-      <c r="B15" s="77"/>
-      <c r="C15" s="77"/>
-      <c r="D15" s="77"/>
-      <c r="E15" s="77"/>
-      <c r="F15" s="77"/>
-      <c r="G15" s="77"/>
-      <c r="H15" s="77"/>
-      <c r="I15" s="77"/>
-      <c r="J15" s="77"/>
-      <c r="K15" s="77"/>
-      <c r="L15" s="77"/>
-      <c r="M15" s="77"/>
-      <c r="N15" s="77"/>
-      <c r="O15" s="77"/>
-      <c r="P15" s="77"/>
-      <c r="Q15" s="77"/>
-      <c r="R15" s="77"/>
-      <c r="S15" s="77"/>
-      <c r="T15" s="77"/>
-      <c r="U15" s="49"/>
-      <c r="V15" s="78"/>
+      <c r="A15" s="109"/>
+      <c r="B15" s="110"/>
+      <c r="C15" s="110"/>
+      <c r="D15" s="110"/>
+      <c r="E15" s="110"/>
+      <c r="F15" s="110"/>
+      <c r="G15" s="110"/>
+      <c r="H15" s="110"/>
+      <c r="I15" s="110"/>
+      <c r="J15" s="110"/>
+      <c r="K15" s="110"/>
+      <c r="L15" s="110"/>
+      <c r="M15" s="110"/>
+      <c r="N15" s="110"/>
+      <c r="O15" s="110"/>
+      <c r="P15" s="110"/>
+      <c r="Q15" s="110"/>
+      <c r="R15" s="110"/>
+      <c r="S15" s="110"/>
+      <c r="T15" s="110"/>
+      <c r="U15" s="60"/>
+      <c r="V15" s="111"/>
     </row>
     <row r="16" spans="1:32" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="76"/>
-      <c r="B16" s="77"/>
-      <c r="C16" s="77"/>
-      <c r="D16" s="77"/>
-      <c r="E16" s="77"/>
-      <c r="F16" s="77"/>
-      <c r="G16" s="77"/>
-      <c r="H16" s="77"/>
-      <c r="I16" s="77"/>
-      <c r="J16" s="77"/>
-      <c r="K16" s="77"/>
-      <c r="L16" s="77"/>
-      <c r="M16" s="77"/>
-      <c r="N16" s="77"/>
-      <c r="O16" s="77"/>
-      <c r="P16" s="77"/>
-      <c r="Q16" s="77"/>
-      <c r="R16" s="77"/>
-      <c r="S16" s="77"/>
-      <c r="T16" s="77"/>
-      <c r="U16" s="49"/>
-      <c r="V16" s="78"/>
+      <c r="A16" s="109"/>
+      <c r="B16" s="110"/>
+      <c r="C16" s="110"/>
+      <c r="D16" s="110"/>
+      <c r="E16" s="110"/>
+      <c r="F16" s="110"/>
+      <c r="G16" s="110"/>
+      <c r="H16" s="110"/>
+      <c r="I16" s="110"/>
+      <c r="J16" s="110"/>
+      <c r="K16" s="110"/>
+      <c r="L16" s="110"/>
+      <c r="M16" s="110"/>
+      <c r="N16" s="110"/>
+      <c r="O16" s="110"/>
+      <c r="P16" s="110"/>
+      <c r="Q16" s="110"/>
+      <c r="R16" s="110"/>
+      <c r="S16" s="110"/>
+      <c r="T16" s="110"/>
+      <c r="U16" s="60"/>
+      <c r="V16" s="111"/>
     </row>
     <row r="17" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="76"/>
-      <c r="B17" s="77"/>
-      <c r="C17" s="77"/>
-      <c r="D17" s="77"/>
-      <c r="E17" s="77"/>
-      <c r="F17" s="77"/>
-      <c r="G17" s="77"/>
-      <c r="H17" s="77"/>
-      <c r="I17" s="77"/>
-      <c r="J17" s="77"/>
-      <c r="K17" s="77"/>
-      <c r="L17" s="77"/>
-      <c r="M17" s="77"/>
-      <c r="N17" s="77"/>
-      <c r="O17" s="77"/>
-      <c r="P17" s="77"/>
-      <c r="Q17" s="77"/>
-      <c r="R17" s="77"/>
-      <c r="S17" s="77"/>
-      <c r="T17" s="77"/>
-      <c r="U17" s="49"/>
-      <c r="V17" s="78"/>
+      <c r="A17" s="109"/>
+      <c r="B17" s="110"/>
+      <c r="C17" s="110"/>
+      <c r="D17" s="110"/>
+      <c r="E17" s="110"/>
+      <c r="F17" s="110"/>
+      <c r="G17" s="110"/>
+      <c r="H17" s="110"/>
+      <c r="I17" s="110"/>
+      <c r="J17" s="110"/>
+      <c r="K17" s="110"/>
+      <c r="L17" s="110"/>
+      <c r="M17" s="110"/>
+      <c r="N17" s="110"/>
+      <c r="O17" s="110"/>
+      <c r="P17" s="110"/>
+      <c r="Q17" s="110"/>
+      <c r="R17" s="110"/>
+      <c r="S17" s="110"/>
+      <c r="T17" s="110"/>
+      <c r="U17" s="60"/>
+      <c r="V17" s="111"/>
     </row>
     <row r="18" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="76"/>
-      <c r="B18" s="77"/>
-      <c r="C18" s="77"/>
-      <c r="D18" s="77"/>
-      <c r="E18" s="77"/>
-      <c r="F18" s="77"/>
-      <c r="G18" s="77"/>
-      <c r="H18" s="77"/>
-      <c r="I18" s="77"/>
-      <c r="J18" s="77"/>
-      <c r="K18" s="77"/>
-      <c r="L18" s="77"/>
-      <c r="M18" s="77"/>
-      <c r="N18" s="77"/>
-      <c r="O18" s="77"/>
-      <c r="P18" s="77"/>
-      <c r="Q18" s="77"/>
-      <c r="R18" s="77"/>
-      <c r="S18" s="77"/>
-      <c r="T18" s="77"/>
-      <c r="U18" s="49"/>
-      <c r="V18" s="78"/>
+      <c r="A18" s="109"/>
+      <c r="B18" s="110"/>
+      <c r="C18" s="110"/>
+      <c r="D18" s="110"/>
+      <c r="E18" s="110"/>
+      <c r="F18" s="110"/>
+      <c r="G18" s="110"/>
+      <c r="H18" s="110"/>
+      <c r="I18" s="110"/>
+      <c r="J18" s="110"/>
+      <c r="K18" s="110"/>
+      <c r="L18" s="110"/>
+      <c r="M18" s="110"/>
+      <c r="N18" s="110"/>
+      <c r="O18" s="110"/>
+      <c r="P18" s="110"/>
+      <c r="Q18" s="110"/>
+      <c r="R18" s="110"/>
+      <c r="S18" s="110"/>
+      <c r="T18" s="110"/>
+      <c r="U18" s="60"/>
+      <c r="V18" s="111"/>
     </row>
     <row r="19" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="76"/>
-      <c r="B19" s="77"/>
-      <c r="C19" s="77"/>
-      <c r="D19" s="77"/>
-      <c r="E19" s="77"/>
-      <c r="F19" s="77"/>
-      <c r="G19" s="77"/>
-      <c r="H19" s="77"/>
-      <c r="I19" s="77"/>
-      <c r="J19" s="77"/>
-      <c r="K19" s="77"/>
-      <c r="L19" s="77"/>
-      <c r="M19" s="77"/>
-      <c r="N19" s="77"/>
-      <c r="O19" s="77"/>
-      <c r="P19" s="77"/>
-      <c r="Q19" s="77"/>
-      <c r="R19" s="77"/>
-      <c r="S19" s="77"/>
-      <c r="T19" s="77"/>
-      <c r="U19" s="49"/>
-      <c r="V19" s="78"/>
+      <c r="A19" s="109"/>
+      <c r="B19" s="110"/>
+      <c r="C19" s="110"/>
+      <c r="D19" s="110"/>
+      <c r="E19" s="110"/>
+      <c r="F19" s="110"/>
+      <c r="G19" s="110"/>
+      <c r="H19" s="110"/>
+      <c r="I19" s="110"/>
+      <c r="J19" s="110"/>
+      <c r="K19" s="110"/>
+      <c r="L19" s="110"/>
+      <c r="M19" s="110"/>
+      <c r="N19" s="110"/>
+      <c r="O19" s="110"/>
+      <c r="P19" s="110"/>
+      <c r="Q19" s="110"/>
+      <c r="R19" s="110"/>
+      <c r="S19" s="110"/>
+      <c r="T19" s="110"/>
+      <c r="U19" s="60"/>
+      <c r="V19" s="111"/>
     </row>
     <row r="20" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="76"/>
-      <c r="B20" s="77"/>
-      <c r="C20" s="77"/>
-      <c r="D20" s="77"/>
-      <c r="E20" s="77"/>
-      <c r="F20" s="77"/>
-      <c r="G20" s="77"/>
-      <c r="H20" s="77"/>
-      <c r="I20" s="77"/>
-      <c r="J20" s="77"/>
-      <c r="K20" s="77"/>
-      <c r="L20" s="77"/>
-      <c r="M20" s="77"/>
-      <c r="N20" s="77"/>
-      <c r="O20" s="77"/>
-      <c r="P20" s="77"/>
-      <c r="Q20" s="77"/>
-      <c r="R20" s="77"/>
-      <c r="S20" s="77"/>
-      <c r="T20" s="77"/>
-      <c r="U20" s="49"/>
-      <c r="V20" s="78"/>
+      <c r="A20" s="109"/>
+      <c r="B20" s="110"/>
+      <c r="C20" s="110"/>
+      <c r="D20" s="110"/>
+      <c r="E20" s="110"/>
+      <c r="F20" s="110"/>
+      <c r="G20" s="110"/>
+      <c r="H20" s="110"/>
+      <c r="I20" s="110"/>
+      <c r="J20" s="110"/>
+      <c r="K20" s="110"/>
+      <c r="L20" s="110"/>
+      <c r="M20" s="110"/>
+      <c r="N20" s="110"/>
+      <c r="O20" s="110"/>
+      <c r="P20" s="110"/>
+      <c r="Q20" s="110"/>
+      <c r="R20" s="110"/>
+      <c r="S20" s="110"/>
+      <c r="T20" s="110"/>
+      <c r="U20" s="60"/>
+      <c r="V20" s="111"/>
     </row>
     <row r="21" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="76"/>
-      <c r="B21" s="77"/>
-      <c r="C21" s="77"/>
-      <c r="D21" s="77"/>
-      <c r="E21" s="77"/>
-      <c r="F21" s="77"/>
-      <c r="G21" s="77"/>
-      <c r="H21" s="77"/>
-      <c r="I21" s="77"/>
-      <c r="J21" s="77"/>
-      <c r="K21" s="77"/>
-      <c r="L21" s="77"/>
-      <c r="M21" s="77"/>
-      <c r="N21" s="77"/>
-      <c r="O21" s="77"/>
-      <c r="P21" s="77"/>
-      <c r="Q21" s="77"/>
-      <c r="R21" s="77"/>
-      <c r="S21" s="77"/>
-      <c r="T21" s="77"/>
-      <c r="U21" s="49"/>
-      <c r="V21" s="78"/>
+      <c r="A21" s="109"/>
+      <c r="B21" s="110"/>
+      <c r="C21" s="110"/>
+      <c r="D21" s="110"/>
+      <c r="E21" s="110"/>
+      <c r="F21" s="110"/>
+      <c r="G21" s="110"/>
+      <c r="H21" s="110"/>
+      <c r="I21" s="110"/>
+      <c r="J21" s="110"/>
+      <c r="K21" s="110"/>
+      <c r="L21" s="110"/>
+      <c r="M21" s="110"/>
+      <c r="N21" s="110"/>
+      <c r="O21" s="110"/>
+      <c r="P21" s="110"/>
+      <c r="Q21" s="110"/>
+      <c r="R21" s="110"/>
+      <c r="S21" s="110"/>
+      <c r="T21" s="110"/>
+      <c r="U21" s="60"/>
+      <c r="V21" s="111"/>
     </row>
     <row r="22" spans="1:22" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="123"/>
-      <c r="B22" s="124"/>
-      <c r="C22" s="124"/>
-      <c r="D22" s="124"/>
-      <c r="E22" s="124"/>
-      <c r="F22" s="124"/>
-      <c r="G22" s="124"/>
-      <c r="H22" s="124"/>
-      <c r="I22" s="124"/>
-      <c r="J22" s="124"/>
-      <c r="K22" s="124"/>
-      <c r="L22" s="124"/>
-      <c r="M22" s="124"/>
-      <c r="N22" s="124"/>
-      <c r="O22" s="124"/>
-      <c r="P22" s="124"/>
-      <c r="Q22" s="124"/>
-      <c r="R22" s="124"/>
-      <c r="S22" s="124"/>
-      <c r="T22" s="124"/>
-      <c r="U22" s="125"/>
-      <c r="V22" s="126"/>
+      <c r="A22" s="112"/>
+      <c r="B22" s="113"/>
+      <c r="C22" s="113"/>
+      <c r="D22" s="113"/>
+      <c r="E22" s="113"/>
+      <c r="F22" s="113"/>
+      <c r="G22" s="113"/>
+      <c r="H22" s="113"/>
+      <c r="I22" s="113"/>
+      <c r="J22" s="113"/>
+      <c r="K22" s="113"/>
+      <c r="L22" s="113"/>
+      <c r="M22" s="113"/>
+      <c r="N22" s="113"/>
+      <c r="O22" s="113"/>
+      <c r="P22" s="113"/>
+      <c r="Q22" s="113"/>
+      <c r="R22" s="113"/>
+      <c r="S22" s="113"/>
+      <c r="T22" s="113"/>
+      <c r="U22" s="114"/>
+      <c r="V22" s="115"/>
     </row>
     <row r="23" spans="1:22" ht="3.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="127" t="s">
+      <c r="A23" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="B23" s="128"/>
-      <c r="C23" s="61" t="s">
+      <c r="B23" s="21"/>
+      <c r="C23" s="34" t="s">
         <v>28</v>
       </c>
-      <c r="D23" s="9"/>
-      <c r="E23" s="9"/>
-      <c r="F23" s="61"/>
-      <c r="G23" s="61" t="s">
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
+      <c r="F23" s="34"/>
+      <c r="G23" s="34" t="s">
         <v>39</v>
       </c>
-      <c r="H23" s="9"/>
-      <c r="I23" s="9"/>
-      <c r="J23" s="61"/>
-      <c r="K23" s="79"/>
-      <c r="L23" s="64" t="s">
+      <c r="H23" s="2"/>
+      <c r="I23" s="2"/>
+      <c r="J23" s="34"/>
+      <c r="K23" s="37"/>
+      <c r="L23" s="34" t="s">
         <v>10</v>
       </c>
-      <c r="M23" s="64"/>
-      <c r="N23" s="64"/>
-      <c r="O23" s="64"/>
-      <c r="P23" s="64"/>
-      <c r="Q23" s="64"/>
-      <c r="R23" s="64"/>
-      <c r="S23" s="64"/>
-      <c r="T23" s="64"/>
-      <c r="U23" s="64"/>
-      <c r="V23" s="65"/>
+      <c r="M23" s="34"/>
+      <c r="N23" s="34"/>
+      <c r="O23" s="34"/>
+      <c r="P23" s="34"/>
+      <c r="Q23" s="34"/>
+      <c r="R23" s="34"/>
+      <c r="S23" s="34"/>
+      <c r="T23" s="34"/>
+      <c r="U23" s="34"/>
+      <c r="V23" s="37"/>
     </row>
     <row r="24" spans="1:22" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="129"/>
-      <c r="B24" s="98"/>
-      <c r="C24" s="62"/>
-      <c r="D24" s="10"/>
-      <c r="E24" s="26"/>
-      <c r="F24" s="62"/>
-      <c r="G24" s="62"/>
-      <c r="H24" s="10"/>
-      <c r="I24" s="26"/>
-      <c r="J24" s="62"/>
-      <c r="K24" s="80"/>
-      <c r="L24" s="66"/>
-      <c r="M24" s="66"/>
-      <c r="N24" s="66"/>
-      <c r="O24" s="66"/>
-      <c r="P24" s="66"/>
-      <c r="Q24" s="66"/>
-      <c r="R24" s="66"/>
-      <c r="S24" s="66"/>
-      <c r="T24" s="66"/>
-      <c r="U24" s="66"/>
-      <c r="V24" s="67"/>
+      <c r="A24" s="22"/>
+      <c r="B24" s="23"/>
+      <c r="C24" s="35"/>
+      <c r="D24" s="3"/>
+      <c r="E24" s="7"/>
+      <c r="F24" s="35"/>
+      <c r="G24" s="35"/>
+      <c r="H24" s="3"/>
+      <c r="I24" s="7"/>
+      <c r="J24" s="35"/>
+      <c r="K24" s="38"/>
+      <c r="L24" s="35"/>
+      <c r="M24" s="35"/>
+      <c r="N24" s="35"/>
+      <c r="O24" s="35"/>
+      <c r="P24" s="35"/>
+      <c r="Q24" s="35"/>
+      <c r="R24" s="35"/>
+      <c r="S24" s="35"/>
+      <c r="T24" s="35"/>
+      <c r="U24" s="35"/>
+      <c r="V24" s="38"/>
     </row>
     <row r="25" spans="1:22" ht="3.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="130"/>
-      <c r="B25" s="101"/>
-      <c r="C25" s="63"/>
-      <c r="D25" s="13"/>
-      <c r="E25" s="13"/>
-      <c r="F25" s="63"/>
-      <c r="G25" s="63"/>
-      <c r="H25" s="13"/>
-      <c r="I25" s="13"/>
-      <c r="J25" s="63"/>
-      <c r="K25" s="81"/>
-      <c r="L25" s="68"/>
-      <c r="M25" s="68"/>
-      <c r="N25" s="68"/>
-      <c r="O25" s="68"/>
-      <c r="P25" s="68"/>
-      <c r="Q25" s="68"/>
-      <c r="R25" s="68"/>
-      <c r="S25" s="68"/>
-      <c r="T25" s="68"/>
-      <c r="U25" s="68"/>
-      <c r="V25" s="69"/>
+      <c r="A25" s="24"/>
+      <c r="B25" s="25"/>
+      <c r="C25" s="36"/>
+      <c r="D25" s="4"/>
+      <c r="E25" s="4"/>
+      <c r="F25" s="36"/>
+      <c r="G25" s="36"/>
+      <c r="H25" s="4"/>
+      <c r="I25" s="4"/>
+      <c r="J25" s="36"/>
+      <c r="K25" s="39"/>
+      <c r="L25" s="116"/>
+      <c r="M25" s="116"/>
+      <c r="N25" s="116"/>
+      <c r="O25" s="116"/>
+      <c r="P25" s="116"/>
+      <c r="Q25" s="116"/>
+      <c r="R25" s="116"/>
+      <c r="S25" s="116"/>
+      <c r="T25" s="116"/>
+      <c r="U25" s="116"/>
+      <c r="V25" s="117"/>
     </row>
     <row r="26" spans="1:22" ht="3" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="82" t="s">
+      <c r="A26" s="118" t="s">
         <v>20</v>
       </c>
-      <c r="B26" s="85" t="s">
+      <c r="B26" s="119" t="s">
         <v>11</v>
       </c>
-      <c r="C26" s="86"/>
-      <c r="D26" s="87"/>
-      <c r="E26" s="85" t="s">
+      <c r="C26" s="120"/>
+      <c r="D26" s="121"/>
+      <c r="E26" s="119" t="s">
         <v>26</v>
       </c>
-      <c r="F26" s="86"/>
-      <c r="G26" s="86"/>
-      <c r="H26" s="87"/>
-      <c r="I26" s="85" t="s">
+      <c r="F26" s="120"/>
+      <c r="G26" s="120"/>
+      <c r="H26" s="121"/>
+      <c r="I26" s="119" t="s">
         <v>21</v>
       </c>
-      <c r="J26" s="86"/>
-      <c r="K26" s="106"/>
-      <c r="L26" s="8"/>
-      <c r="M26" s="8"/>
-      <c r="N26" s="131" t="s">
+      <c r="J26" s="120"/>
+      <c r="K26" s="122"/>
+      <c r="L26" s="9"/>
+      <c r="M26" s="9"/>
+      <c r="N26" s="26" t="s">
         <v>40</v>
       </c>
-      <c r="O26" s="131"/>
-      <c r="P26" s="132"/>
-      <c r="Q26" s="27"/>
-      <c r="R26" s="25"/>
-      <c r="S26" s="25"/>
-      <c r="T26" s="25"/>
-      <c r="U26" s="25"/>
+      <c r="O26" s="26"/>
+      <c r="P26" s="27"/>
+      <c r="Q26" s="12"/>
+      <c r="R26" s="10"/>
+      <c r="S26" s="10"/>
+      <c r="T26" s="10"/>
+      <c r="U26" s="10"/>
       <c r="V26" s="11"/>
     </row>
     <row r="27" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="83"/>
-      <c r="B27" s="88"/>
-      <c r="C27" s="66"/>
-      <c r="D27" s="89"/>
-      <c r="E27" s="88"/>
-      <c r="F27" s="66"/>
-      <c r="G27" s="66"/>
-      <c r="H27" s="89"/>
-      <c r="I27" s="88"/>
-      <c r="J27" s="66"/>
-      <c r="K27" s="67"/>
-      <c r="L27" s="28" t="s">
+      <c r="A27" s="123"/>
+      <c r="B27" s="124"/>
+      <c r="C27" s="35"/>
+      <c r="D27" s="125"/>
+      <c r="E27" s="124"/>
+      <c r="F27" s="35"/>
+      <c r="G27" s="35"/>
+      <c r="H27" s="125"/>
+      <c r="I27" s="124"/>
+      <c r="J27" s="35"/>
+      <c r="K27" s="38"/>
+      <c r="L27" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="M27" s="14"/>
-      <c r="N27" s="96"/>
-      <c r="O27" s="96"/>
-      <c r="P27" s="97"/>
-      <c r="Q27" s="27"/>
-      <c r="R27" s="14" t="s">
+      <c r="M27" s="5"/>
+      <c r="N27" s="28"/>
+      <c r="O27" s="28"/>
+      <c r="P27" s="29"/>
+      <c r="Q27" s="12"/>
+      <c r="R27" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="S27" s="96" t="s">
+      <c r="S27" s="28" t="s">
         <v>40</v>
       </c>
-      <c r="T27" s="96"/>
-      <c r="U27" s="96"/>
-      <c r="V27" s="97"/>
+      <c r="T27" s="28"/>
+      <c r="U27" s="28"/>
+      <c r="V27" s="29"/>
     </row>
     <row r="28" spans="1:22" ht="3" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="84"/>
-      <c r="B28" s="90"/>
-      <c r="C28" s="91"/>
-      <c r="D28" s="92"/>
-      <c r="E28" s="90"/>
-      <c r="F28" s="91"/>
-      <c r="G28" s="91"/>
-      <c r="H28" s="92"/>
-      <c r="I28" s="90"/>
-      <c r="J28" s="91"/>
-      <c r="K28" s="107"/>
-      <c r="L28" s="16"/>
-      <c r="M28" s="16"/>
-      <c r="N28" s="133"/>
-      <c r="O28" s="133"/>
-      <c r="P28" s="134"/>
+      <c r="A28" s="126"/>
+      <c r="B28" s="127"/>
+      <c r="C28" s="36"/>
+      <c r="D28" s="128"/>
+      <c r="E28" s="127"/>
+      <c r="F28" s="36"/>
+      <c r="G28" s="36"/>
+      <c r="H28" s="128"/>
+      <c r="I28" s="127"/>
+      <c r="J28" s="36"/>
+      <c r="K28" s="39"/>
+      <c r="L28" s="6"/>
+      <c r="M28" s="6"/>
+      <c r="N28" s="30"/>
+      <c r="O28" s="30"/>
+      <c r="P28" s="31"/>
       <c r="Q28" s="17"/>
-      <c r="R28" s="16"/>
+      <c r="R28" s="6"/>
       <c r="S28" s="17"/>
       <c r="T28" s="17"/>
       <c r="U28" s="17"/>
       <c r="V28" s="18"/>
     </row>
     <row r="29" spans="1:22" ht="3" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="82"/>
-      <c r="B29" s="85"/>
-      <c r="C29" s="86"/>
-      <c r="D29" s="87"/>
-      <c r="E29" s="85"/>
-      <c r="F29" s="86"/>
-      <c r="G29" s="86"/>
-      <c r="H29" s="87"/>
-      <c r="I29" s="85"/>
-      <c r="J29" s="86"/>
-      <c r="K29" s="106"/>
-      <c r="L29" s="28"/>
-      <c r="M29" s="28"/>
-      <c r="N29" s="98" t="s">
+      <c r="A29" s="118"/>
+      <c r="B29" s="119"/>
+      <c r="C29" s="120"/>
+      <c r="D29" s="121"/>
+      <c r="E29" s="119"/>
+      <c r="F29" s="120"/>
+      <c r="G29" s="120"/>
+      <c r="H29" s="121"/>
+      <c r="I29" s="119"/>
+      <c r="J29" s="120"/>
+      <c r="K29" s="122"/>
+      <c r="L29" s="8"/>
+      <c r="M29" s="8"/>
+      <c r="N29" s="23" t="s">
         <v>41</v>
       </c>
-      <c r="O29" s="98"/>
-      <c r="P29" s="99"/>
-      <c r="Q29" s="24"/>
-      <c r="R29" s="28"/>
-      <c r="S29" s="27"/>
-      <c r="T29" s="27"/>
-      <c r="U29" s="27"/>
-      <c r="V29" s="15"/>
+      <c r="O29" s="23"/>
+      <c r="P29" s="32"/>
+      <c r="Q29" s="14"/>
+      <c r="R29" s="8"/>
+      <c r="S29" s="12"/>
+      <c r="T29" s="12"/>
+      <c r="U29" s="12"/>
+      <c r="V29" s="13"/>
     </row>
     <row r="30" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="83"/>
-      <c r="B30" s="88"/>
-      <c r="C30" s="66"/>
-      <c r="D30" s="89"/>
-      <c r="E30" s="88"/>
-      <c r="F30" s="66"/>
-      <c r="G30" s="66"/>
-      <c r="H30" s="89"/>
-      <c r="I30" s="88"/>
-      <c r="J30" s="66"/>
-      <c r="K30" s="67"/>
-      <c r="L30" s="26" t="s">
+      <c r="A30" s="123"/>
+      <c r="B30" s="124"/>
+      <c r="C30" s="35"/>
+      <c r="D30" s="125"/>
+      <c r="E30" s="124"/>
+      <c r="F30" s="35"/>
+      <c r="G30" s="35"/>
+      <c r="H30" s="125"/>
+      <c r="I30" s="124"/>
+      <c r="J30" s="35"/>
+      <c r="K30" s="38"/>
+      <c r="L30" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="M30" s="10"/>
-      <c r="N30" s="98"/>
-      <c r="O30" s="98"/>
-      <c r="P30" s="99"/>
-      <c r="Q30" s="24"/>
-      <c r="R30" s="10" t="s">
+      <c r="M30" s="3"/>
+      <c r="N30" s="23"/>
+      <c r="O30" s="23"/>
+      <c r="P30" s="32"/>
+      <c r="Q30" s="14"/>
+      <c r="R30" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="S30" s="98" t="s">
+      <c r="S30" s="23" t="s">
         <v>41</v>
       </c>
-      <c r="T30" s="98"/>
-      <c r="U30" s="98"/>
-      <c r="V30" s="99"/>
+      <c r="T30" s="23"/>
+      <c r="U30" s="23"/>
+      <c r="V30" s="32"/>
     </row>
     <row r="31" spans="1:22" ht="3.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="83"/>
-      <c r="B31" s="88"/>
-      <c r="C31" s="66"/>
-      <c r="D31" s="89"/>
-      <c r="E31" s="88"/>
-      <c r="F31" s="66"/>
-      <c r="G31" s="66"/>
-      <c r="H31" s="89"/>
-      <c r="I31" s="88"/>
-      <c r="J31" s="66"/>
-      <c r="K31" s="67"/>
-      <c r="L31" s="13"/>
-      <c r="M31" s="13"/>
-      <c r="N31" s="101"/>
-      <c r="O31" s="101"/>
-      <c r="P31" s="102"/>
-      <c r="Q31" s="12"/>
-      <c r="R31" s="13"/>
-      <c r="S31" s="13"/>
-      <c r="T31" s="12"/>
-      <c r="U31" s="12"/>
-      <c r="V31" s="19"/>
+      <c r="A31" s="123"/>
+      <c r="B31" s="124"/>
+      <c r="C31" s="35"/>
+      <c r="D31" s="125"/>
+      <c r="E31" s="124"/>
+      <c r="F31" s="35"/>
+      <c r="G31" s="35"/>
+      <c r="H31" s="125"/>
+      <c r="I31" s="124"/>
+      <c r="J31" s="35"/>
+      <c r="K31" s="38"/>
+      <c r="L31" s="4"/>
+      <c r="M31" s="4"/>
+      <c r="N31" s="25"/>
+      <c r="O31" s="25"/>
+      <c r="P31" s="33"/>
+      <c r="Q31" s="15"/>
+      <c r="R31" s="4"/>
+      <c r="S31" s="4"/>
+      <c r="T31" s="15"/>
+      <c r="U31" s="15"/>
+      <c r="V31" s="16"/>
     </row>
     <row r="32" spans="1:22" ht="69" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="84"/>
-      <c r="B32" s="90"/>
-      <c r="C32" s="91"/>
-      <c r="D32" s="92"/>
-      <c r="E32" s="90"/>
-      <c r="F32" s="91"/>
-      <c r="G32" s="91"/>
-      <c r="H32" s="92"/>
-      <c r="I32" s="90"/>
-      <c r="J32" s="91"/>
-      <c r="K32" s="107"/>
-      <c r="L32" s="91"/>
-      <c r="M32" s="91"/>
-      <c r="N32" s="91"/>
-      <c r="O32" s="91"/>
-      <c r="P32" s="107"/>
-      <c r="Q32" s="103"/>
-      <c r="R32" s="104"/>
-      <c r="S32" s="104"/>
-      <c r="T32" s="104"/>
-      <c r="U32" s="104"/>
-      <c r="V32" s="105"/>
-    </row>
-    <row r="33" spans="1:24" s="5" customFormat="1" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="20" t="s">
+      <c r="A32" s="126"/>
+      <c r="B32" s="127"/>
+      <c r="C32" s="36"/>
+      <c r="D32" s="128"/>
+      <c r="E32" s="127"/>
+      <c r="F32" s="36"/>
+      <c r="G32" s="36"/>
+      <c r="H32" s="128"/>
+      <c r="I32" s="127"/>
+      <c r="J32" s="36"/>
+      <c r="K32" s="39"/>
+      <c r="L32" s="36"/>
+      <c r="M32" s="36"/>
+      <c r="N32" s="36"/>
+      <c r="O32" s="36"/>
+      <c r="P32" s="39"/>
+      <c r="Q32" s="129"/>
+      <c r="R32" s="58"/>
+      <c r="S32" s="58"/>
+      <c r="T32" s="58"/>
+      <c r="U32" s="58"/>
+      <c r="V32" s="130"/>
+    </row>
+    <row r="33" spans="1:24" s="139" customFormat="1" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="131" t="s">
         <v>12</v>
       </c>
-      <c r="B33" s="100" t="s">
+      <c r="B33" s="132" t="s">
         <v>29</v>
       </c>
-      <c r="C33" s="68"/>
-      <c r="D33" s="68"/>
-      <c r="E33" s="100" t="s">
+      <c r="C33" s="116"/>
+      <c r="D33" s="116"/>
+      <c r="E33" s="132" t="s">
         <v>36</v>
       </c>
-      <c r="F33" s="68"/>
-      <c r="G33" s="68"/>
-      <c r="H33" s="135"/>
-      <c r="I33" s="100" t="s">
+      <c r="F33" s="116"/>
+      <c r="G33" s="116"/>
+      <c r="H33" s="133"/>
+      <c r="I33" s="132" t="s">
         <v>30</v>
       </c>
-      <c r="J33" s="68"/>
-      <c r="K33" s="69"/>
-      <c r="L33" s="136" t="s">
+      <c r="J33" s="116"/>
+      <c r="K33" s="117"/>
+      <c r="L33" s="134" t="s">
         <v>31</v>
       </c>
-      <c r="M33" s="136"/>
-      <c r="N33" s="136"/>
-      <c r="O33" s="136"/>
-      <c r="P33" s="137"/>
-      <c r="Q33" s="93" t="s">
+      <c r="M33" s="134"/>
+      <c r="N33" s="134"/>
+      <c r="O33" s="134"/>
+      <c r="P33" s="135"/>
+      <c r="Q33" s="136" t="s">
         <v>34</v>
       </c>
-      <c r="R33" s="94"/>
-      <c r="S33" s="94"/>
-      <c r="T33" s="94"/>
-      <c r="U33" s="94"/>
-      <c r="V33" s="95"/>
+      <c r="R33" s="137"/>
+      <c r="S33" s="137"/>
+      <c r="T33" s="137"/>
+      <c r="U33" s="137"/>
+      <c r="V33" s="138"/>
     </row>
     <row r="34" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="122" t="s">
+      <c r="A34" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="B34" s="122"/>
-      <c r="C34" s="122"/>
-      <c r="D34" s="122"/>
-      <c r="E34" s="122"/>
-      <c r="F34" s="122"/>
-      <c r="G34" s="122"/>
-      <c r="H34" s="122"/>
-      <c r="I34" s="122"/>
-      <c r="J34" s="122"/>
-      <c r="K34" s="122"/>
-      <c r="L34" s="122"/>
-      <c r="M34" s="122"/>
-      <c r="N34" s="122"/>
-      <c r="O34" s="122"/>
-      <c r="P34" s="122"/>
-      <c r="Q34" s="122"/>
-      <c r="R34" s="122"/>
-      <c r="S34" s="122"/>
-      <c r="T34" s="122"/>
-      <c r="U34" s="122"/>
-      <c r="V34" s="122"/>
-      <c r="W34" s="1"/>
-      <c r="X34" s="1"/>
+      <c r="B34" s="19"/>
+      <c r="C34" s="19"/>
+      <c r="D34" s="19"/>
+      <c r="E34" s="19"/>
+      <c r="F34" s="19"/>
+      <c r="G34" s="19"/>
+      <c r="H34" s="19"/>
+      <c r="I34" s="19"/>
+      <c r="J34" s="19"/>
+      <c r="K34" s="19"/>
+      <c r="L34" s="19"/>
+      <c r="M34" s="19"/>
+      <c r="N34" s="19"/>
+      <c r="O34" s="19"/>
+      <c r="P34" s="19"/>
+      <c r="Q34" s="19"/>
+      <c r="R34" s="19"/>
+      <c r="S34" s="19"/>
+      <c r="T34" s="19"/>
+      <c r="U34" s="19"/>
+      <c r="V34" s="19"/>
+      <c r="W34" s="140"/>
+      <c r="X34" s="140"/>
     </row>
     <row r="35" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="122" t="s">
+      <c r="A35" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="B35" s="122"/>
-      <c r="C35" s="122"/>
-      <c r="D35" s="122"/>
-      <c r="E35" s="122"/>
-      <c r="F35" s="122"/>
-      <c r="G35" s="122"/>
-      <c r="H35" s="122"/>
-      <c r="I35" s="122"/>
-      <c r="J35" s="122"/>
-      <c r="K35" s="122"/>
-      <c r="L35" s="122"/>
-      <c r="M35" s="122"/>
-      <c r="N35" s="122"/>
-      <c r="O35" s="122"/>
-      <c r="P35" s="122"/>
-      <c r="Q35" s="122"/>
-      <c r="R35" s="122"/>
-      <c r="S35" s="122"/>
-      <c r="T35" s="122"/>
-      <c r="U35" s="122"/>
-      <c r="V35" s="122"/>
-      <c r="W35" s="1"/>
-      <c r="X35" s="1"/>
-    </row>
-    <row r="36" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A36" s="6"/>
-      <c r="B36" s="6"/>
-      <c r="C36" s="6"/>
-      <c r="D36" s="6"/>
-      <c r="E36" s="6"/>
-      <c r="F36" s="6"/>
-      <c r="G36" s="6"/>
-      <c r="H36" s="6"/>
-      <c r="I36" s="6"/>
-      <c r="J36" s="6"/>
-      <c r="K36" s="6"/>
-      <c r="L36" s="6"/>
-      <c r="M36" s="6"/>
-      <c r="N36" s="6"/>
-      <c r="O36" s="6"/>
-      <c r="P36" s="6"/>
-      <c r="Q36" s="6"/>
-      <c r="R36" s="6"/>
-      <c r="S36" s="6"/>
-      <c r="T36" s="6"/>
-      <c r="U36" s="6"/>
-      <c r="V36" s="6"/>
+      <c r="B35" s="19"/>
+      <c r="C35" s="19"/>
+      <c r="D35" s="19"/>
+      <c r="E35" s="19"/>
+      <c r="F35" s="19"/>
+      <c r="G35" s="19"/>
+      <c r="H35" s="19"/>
+      <c r="I35" s="19"/>
+      <c r="J35" s="19"/>
+      <c r="K35" s="19"/>
+      <c r="L35" s="19"/>
+      <c r="M35" s="19"/>
+      <c r="N35" s="19"/>
+      <c r="O35" s="19"/>
+      <c r="P35" s="19"/>
+      <c r="Q35" s="19"/>
+      <c r="R35" s="19"/>
+      <c r="S35" s="19"/>
+      <c r="T35" s="19"/>
+      <c r="U35" s="19"/>
+      <c r="V35" s="19"/>
+      <c r="W35" s="140"/>
+      <c r="X35" s="140"/>
     </row>
   </sheetData>
   <mergeCells count="78">
+    <mergeCell ref="T3:U3"/>
+    <mergeCell ref="A3:S3"/>
+    <mergeCell ref="C8:K8"/>
+    <mergeCell ref="C10:K10"/>
+    <mergeCell ref="C9:K9"/>
+    <mergeCell ref="Q4:S4"/>
+    <mergeCell ref="Q5:S5"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="O5:P5"/>
+    <mergeCell ref="L10:O10"/>
+    <mergeCell ref="O4:P4"/>
+    <mergeCell ref="P9:V9"/>
+    <mergeCell ref="G23:G25"/>
+    <mergeCell ref="L23:V25"/>
+    <mergeCell ref="P10:V10"/>
+    <mergeCell ref="L11:O11"/>
+    <mergeCell ref="P11:V11"/>
+    <mergeCell ref="L12:O12"/>
+    <mergeCell ref="A14:V14"/>
+    <mergeCell ref="A15:V15"/>
+    <mergeCell ref="F23:F25"/>
+    <mergeCell ref="P12:V12"/>
+    <mergeCell ref="J23:K25"/>
+    <mergeCell ref="A18:V18"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="C23:C25"/>
+    <mergeCell ref="A16:V16"/>
+    <mergeCell ref="A29:A32"/>
+    <mergeCell ref="B29:D32"/>
+    <mergeCell ref="E29:H32"/>
+    <mergeCell ref="A26:A28"/>
+    <mergeCell ref="B26:D28"/>
+    <mergeCell ref="E26:H28"/>
+    <mergeCell ref="A13:V13"/>
+    <mergeCell ref="A19:V19"/>
+    <mergeCell ref="A17:V17"/>
+    <mergeCell ref="C11:K11"/>
+    <mergeCell ref="C12:K12"/>
+    <mergeCell ref="Q33:V33"/>
+    <mergeCell ref="S27:V27"/>
+    <mergeCell ref="S30:V30"/>
+    <mergeCell ref="I33:K33"/>
+    <mergeCell ref="N29:P31"/>
+    <mergeCell ref="Q32:V32"/>
+    <mergeCell ref="I26:K28"/>
+    <mergeCell ref="L32:P32"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="P6:V6"/>
+    <mergeCell ref="L8:O8"/>
+    <mergeCell ref="B6:N6"/>
+    <mergeCell ref="P8:V8"/>
+    <mergeCell ref="A7:V7"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="L4:N4"/>
+    <mergeCell ref="L5:N5"/>
+    <mergeCell ref="G4:K4"/>
+    <mergeCell ref="G5:K5"/>
     <mergeCell ref="A1:V1"/>
     <mergeCell ref="A2:V2"/>
     <mergeCell ref="A34:V34"/>
@@ -2708,68 +2721,6 @@
     <mergeCell ref="T5:V5"/>
     <mergeCell ref="T4:V4"/>
     <mergeCell ref="L9:O9"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="L4:N4"/>
-    <mergeCell ref="L5:N5"/>
-    <mergeCell ref="G4:K4"/>
-    <mergeCell ref="G5:K5"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="P6:V6"/>
-    <mergeCell ref="L8:O8"/>
-    <mergeCell ref="B6:N6"/>
-    <mergeCell ref="P8:V8"/>
-    <mergeCell ref="A7:V7"/>
-    <mergeCell ref="Q33:V33"/>
-    <mergeCell ref="S27:V27"/>
-    <mergeCell ref="S30:V30"/>
-    <mergeCell ref="I33:K33"/>
-    <mergeCell ref="N29:P31"/>
-    <mergeCell ref="Q32:V32"/>
-    <mergeCell ref="I26:K28"/>
-    <mergeCell ref="L32:P32"/>
-    <mergeCell ref="A13:V13"/>
-    <mergeCell ref="A19:V19"/>
-    <mergeCell ref="A17:V17"/>
-    <mergeCell ref="C11:K11"/>
-    <mergeCell ref="C12:K12"/>
-    <mergeCell ref="A29:A32"/>
-    <mergeCell ref="B29:D32"/>
-    <mergeCell ref="E29:H32"/>
-    <mergeCell ref="A26:A28"/>
-    <mergeCell ref="B26:D28"/>
-    <mergeCell ref="E26:H28"/>
-    <mergeCell ref="G23:G25"/>
-    <mergeCell ref="L23:V25"/>
-    <mergeCell ref="P10:V10"/>
-    <mergeCell ref="L11:O11"/>
-    <mergeCell ref="P11:V11"/>
-    <mergeCell ref="L12:O12"/>
-    <mergeCell ref="A14:V14"/>
-    <mergeCell ref="A15:V15"/>
-    <mergeCell ref="F23:F25"/>
-    <mergeCell ref="P12:V12"/>
-    <mergeCell ref="J23:K25"/>
-    <mergeCell ref="A18:V18"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="C23:C25"/>
-    <mergeCell ref="A16:V16"/>
-    <mergeCell ref="T3:U3"/>
-    <mergeCell ref="A3:S3"/>
-    <mergeCell ref="C8:K8"/>
-    <mergeCell ref="C10:K10"/>
-    <mergeCell ref="C9:K9"/>
-    <mergeCell ref="Q4:S4"/>
-    <mergeCell ref="Q5:S5"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="O5:P5"/>
-    <mergeCell ref="L10:O10"/>
-    <mergeCell ref="O4:P4"/>
-    <mergeCell ref="P9:V9"/>
   </mergeCells>
   <pageMargins left="0.27559055118110237" right="0.19685039370078741" top="0.59055118110236227" bottom="0" header="0.19685039370078741" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="72" orientation="landscape" r:id="rId1"/>
